--- a/main/banco_de_dados/banco.xlsx
+++ b/main/banco_de_dados/banco.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6" outlineLevelCol="0"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="27" min="1" max="1"/>
@@ -832,6 +832,36 @@
       <c r="C9" s="22" t="inlineStr">
         <is>
           <t>souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>teste1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>tetste1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>teste2@teste.com</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -847,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6" outlineLevelCol="0"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="27" min="1" max="1"/>
@@ -1077,6 +1107,60 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>uva</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>uva</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>melancia</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
